--- a/data/trans_orig/IP1011-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1011-Habitat-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>135257</t>
+          <t>136267</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>150058</t>
+          <t>150039</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>287550</t>
+          <t>287535</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>191187</t>
+          <t>191837</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>208125</t>
+          <t>208799</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>402655</t>
+          <t>402805</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>204300</t>
+          <t>204325</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>413623</t>
+          <t>413203</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>677099</t>
+          <t>675887</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>717450</t>
+          <t>717388</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1396659</t>
+          <t>1396170</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1402448</t>
+          <t>1402511</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132570</t>
+          <t>132102</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>150262</t>
+          <t>150071</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>285140</t>
+          <t>284520</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151325</t>
+          <t>151364</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>317464</t>
+          <t>317556</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>203657</t>
+          <t>203137</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>414027</t>
+          <t>413823</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>701965</t>
+          <t>702115</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>743501</t>
+          <t>743100</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1448261</t>
+          <t>1448131</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1454396</t>
+          <t>1454409</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>201702</t>
+          <t>202850</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>409387</t>
+          <t>409580</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>741281</t>
+          <t>741966</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1445116</t>
+          <t>1445301</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP1011-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1011-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -727,102 +727,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3463</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>605</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2459</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3441</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3038</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1207</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4268</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>152475</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>149614</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,74%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>138121</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>136267</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>135285</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,56%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>98,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,52%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>152475</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>150039</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>98,02%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>427</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>287535</t>
+          <t>288150</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1070,102 +1070,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4017</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3326</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3298</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1328</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3343</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4641</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>211475</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>208125</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,69%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,11%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>194502</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>191837</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>191865</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,3%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>211475</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>208799</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,69%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,42%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>632</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>402805</t>
+          <t>402664</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3506</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3499</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3508</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3936</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>207124</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>204318</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>207124</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>204325</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>413203</t>
+          <t>413631</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5849</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1266</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5134</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4386</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5312</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>720730</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>716851</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>722099</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>679755</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>675887</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>676635</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>720730</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>717388</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>722098</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2099</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1396170</t>
+          <t>1396010</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1402511</t>
+          <t>1402455</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2674,102 +2674,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3299</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>756</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4289</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3066</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1407</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3027</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5037</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1407</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4969</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -2782,74 +2782,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>152447</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>149799</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>135635</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>132102</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>133325</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,45%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,86%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,75%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>152447</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>150071</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>98,02%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>392</t>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>284520</t>
+          <t>284452</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3125,47 +3125,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,107 +3355,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3475</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3317</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3295</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3268</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154183</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>151364</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>151522</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,58%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,86%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>495</t>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>317556</t>
+          <t>317529</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,107 +3698,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3371</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>672</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3945</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3423</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3559</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>206410</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>203711</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>206410</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>203137</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>413823</t>
+          <t>413959</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4046,67 +4046,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4606</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>1412</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4369</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5042</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>673</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>746819</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>743536</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,38%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>705516</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>702115</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>702559</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,8%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,38%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>746819</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>743100</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2080</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1448131</t>
+          <t>1448287</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1454409</t>
+          <t>1454397</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4729,47 +4729,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5072,47 +5072,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5415,47 +5415,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,107 +5645,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3095</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4273</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3576</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>205023</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>202641</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>205023</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>202850</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>409580</t>
+          <t>408883</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,107 +5988,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3938</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2878</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3553</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3914</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>744131</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>740906</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>744131</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>741966</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1445301</t>
+          <t>1445662</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
